--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Encounter, Variation Inpatient (PTF)</t>
+    <t>This StructureDefinition contains the maps for VistA PTF (file 45) to FHIR Encounter</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4114" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4113" uniqueCount="612">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1492,6 +1492,9 @@
   </si>
   <si>
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VFSourceOfAdmission</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -11585,13 +11588,11 @@
         <v>40</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>40</v>
+        <v>459</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>40</v>
@@ -11609,7 +11610,7 @@
         <v>40</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>38</v>
@@ -11627,27 +11628,27 @@
         <v>40</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11762,10 +11763,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11882,10 +11883,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11911,16 +11912,16 @@
         <v>62</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>40</v>
@@ -11969,7 +11970,7 @@
         <v>40</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>38</v>
@@ -11987,13 +11988,13 @@
         <v>40</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>40</v>
@@ -12004,10 +12005,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12033,13 +12034,13 @@
         <v>114</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12089,7 +12090,7 @@
         <v>40</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>38</v>
@@ -12107,13 +12108,13 @@
         <v>40</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>40</v>
@@ -12124,10 +12125,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12153,14 +12154,14 @@
         <v>68</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>40</v>
@@ -12209,7 +12210,7 @@
         <v>40</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>38</v>
@@ -12227,27 +12228,27 @@
         <v>40</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12273,14 +12274,14 @@
         <v>114</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>40</v>
@@ -12329,7 +12330,7 @@
         <v>40</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>38</v>
@@ -12347,13 +12348,13 @@
         <v>40</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>40</v>
@@ -12364,10 +12365,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12390,19 +12391,19 @@
         <v>49</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>40</v>
@@ -12451,7 +12452,7 @@
         <v>40</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>38</v>
@@ -12469,13 +12470,13 @@
         <v>40</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>40</v>
@@ -12486,10 +12487,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12515,16 +12516,16 @@
         <v>114</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>40</v>
@@ -12573,7 +12574,7 @@
         <v>40</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>38</v>
@@ -12591,13 +12592,13 @@
         <v>40</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>40</v>
@@ -12608,10 +12609,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12637,10 +12638,10 @@
         <v>136</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12670,10 +12671,10 @@
         <v>242</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>40</v>
@@ -12691,7 +12692,7 @@
         <v>40</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>38</v>
@@ -12715,7 +12716,7 @@
         <v>40</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>40</v>
@@ -12726,10 +12727,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12755,16 +12756,16 @@
         <v>136</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>40</v>
@@ -12792,10 +12793,10 @@
         <v>242</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>40</v>
@@ -12813,7 +12814,7 @@
         <v>40</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>38</v>
@@ -12831,13 +12832,13 @@
         <v>40</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>40</v>
@@ -12848,10 +12849,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12877,10 +12878,10 @@
         <v>136</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12910,10 +12911,10 @@
         <v>72</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>40</v>
@@ -12931,7 +12932,7 @@
         <v>40</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>38</v>
@@ -12949,13 +12950,13 @@
         <v>40</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>40</v>
@@ -12966,10 +12967,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12995,10 +12996,10 @@
         <v>136</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13028,10 +13029,10 @@
         <v>72</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>40</v>
@@ -13049,7 +13050,7 @@
         <v>40</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>38</v>
@@ -13067,13 +13068,13 @@
         <v>40</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>40</v>
@@ -13084,10 +13085,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13113,10 +13114,10 @@
         <v>413</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13167,7 +13168,7 @@
         <v>40</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>38</v>
@@ -13185,13 +13186,13 @@
         <v>40</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>40</v>
@@ -13202,10 +13203,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13320,10 +13321,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13440,10 +13441,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13560,10 +13561,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13680,10 +13681,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13800,10 +13801,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13912,18 +13913,18 @@
         <v>40</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13949,10 +13950,10 @@
         <v>136</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13982,10 +13983,10 @@
         <v>72</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>40</v>
@@ -14003,7 +14004,7 @@
         <v>40</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>38</v>
@@ -14021,27 +14022,27 @@
         <v>40</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14067,13 +14068,13 @@
         <v>193</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14123,7 +14124,7 @@
         <v>40</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>38</v>
@@ -14141,7 +14142,7 @@
         <v>40</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>40</v>
@@ -14158,10 +14159,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14276,10 +14277,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14396,10 +14397,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14518,10 +14519,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14544,13 +14545,13 @@
         <v>40</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14601,7 +14602,7 @@
         <v>40</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>48</v>
@@ -14616,30 +14617,30 @@
         <v>60</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>306</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14665,13 +14666,13 @@
         <v>68</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14700,10 +14701,10 @@
         <v>130</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>40</v>
@@ -14721,7 +14722,7 @@
         <v>40</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>38</v>
@@ -14739,7 +14740,7 @@
         <v>40</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>40</v>
@@ -14756,10 +14757,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14785,13 +14786,13 @@
         <v>136</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14820,10 +14821,10 @@
         <v>242</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>40</v>
@@ -14841,7 +14842,7 @@
         <v>40</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>38</v>
@@ -14876,10 +14877,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14905,10 +14906,10 @@
         <v>166</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14959,7 +14960,7 @@
         <v>40</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>38</v>
@@ -14994,10 +14995,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15020,13 +15021,13 @@
         <v>40</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15077,7 +15078,7 @@
         <v>40</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>38</v>
@@ -15095,27 +15096,27 @@
         <v>305</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15138,16 +15139,16 @@
         <v>40</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15197,7 +15198,7 @@
         <v>40</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>38</v>
@@ -15212,10 +15213,10 @@
         <v>60</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>40</v>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4155" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4155" uniqueCount="656">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -249,10 +249,10 @@
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t xml:space="preserve">Visit
@@ -651,6 +651,9 @@
   </si>
   <si>
     <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>428: source value from PTF - INTERNAL ADMISSION # (#45-2.1)</t>
   </si>
   <si>
     <t>Inpat.Census.AdmitEligibilityIEN
@@ -658,9 +661,6 @@
 Inpat.InpatientFeeBasis.AdmitEligibilityIEN</t>
   </si>
   <si>
-    <t>428: source value from PTF - INTERNAL ADMISSION # (#45-2.1)</t>
-  </si>
-  <si>
     <t>Encounter.identifier.period</t>
   </si>
   <si>
@@ -726,6 +726,10 @@
     <t>http://hl7.org/fhir/ValueSet/encounter-status|4.0.1</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-5:435: fixed value "finished" {null}</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -736,6 +740,9 @@
   </si>
   <si>
     <t>No clear equivalent in HL7 v2; active/finished could be inferred from PV1-44, PV1-45, PV2-24; inactive could be inferred from PV2-16</t>
+  </si>
+  <si>
+    <t>435: fixed value = finished if PTF - DISCHARGE DATE (#45-70) case not null</t>
   </si>
   <si>
     <t>Inpat.Census.CensusDateTime
@@ -757,9 +764,6 @@
 Inpat.InpatientSurgicalProcedure.DischargeDateTime</t>
   </si>
   <si>
-    <t>435: fixed value = finished if PTF - DISCHARGE DATE (#45-70) case not null</t>
-  </si>
-  <si>
     <t>Encounter.statusHistory</t>
   </si>
   <si>
@@ -830,6 +834,10 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-4:1601: fixed value "http://terminology.hl7.org/CodeSystem/v3-ActCode|IMP" {null}</t>
+  </si>
+  <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
   </si>
   <si>
@@ -977,6 +985,9 @@
   </si>
   <si>
     <t>PID-3</t>
+  </si>
+  <si>
+    <t>441: source value from PTF - PATIENT (#45-.01)</t>
   </si>
   <si>
     <t>Inpat.Census.PatientIEN
@@ -995,9 +1006,6 @@
 Inpat.PresentOnAdmission.PatientIEN</t>
   </si>
   <si>
-    <t>441: source value from PTF - PATIENT (#45-.01)</t>
-  </si>
-  <si>
     <t>Encounter.episodeOfCare</t>
   </si>
   <si>
@@ -1213,6 +1221,9 @@
   </si>
   <si>
     <t>DR.1</t>
+  </si>
+  <si>
+    <t>445: source value from PTF - ADMISSION DATE (#45-2)</t>
   </si>
   <si>
     <t>Inpat.Census.AdmitDateTime
@@ -1234,9 +1245,6 @@
 Inpat.InpatientSurgicalProcedure.AdmitDateTime</t>
   </si>
   <si>
-    <t>445: source value from PTF - ADMISSION DATE (#45-2)</t>
-  </si>
-  <si>
     <t>Encounter.period.end</t>
   </si>
   <si>
@@ -1320,10 +1328,10 @@
     <t>EVN-4 / PV2-3 (note: PV2-3 is nominally constrained to inpatient admissions; HL7 v2 makes no vocabulary suggestions for PV2-3; would not expect PV2 segment or PV2-3 to be in use in all implementations )</t>
   </si>
   <si>
+    <t>450: source value from PTF - PROCEDURE [#] (#45-45.01)</t>
+  </si>
+  <si>
     <t>Inpat.InpatientDiagnosis.ICDIEN</t>
-  </si>
-  <si>
-    <t>450: source value from PTF - PROCEDURE [#] (#45-45.01)</t>
   </si>
   <si>
     <t>Encounter.reasonReference</t>
@@ -1570,14 +1578,14 @@
     <t>Reference.display</t>
   </si>
   <si>
+    <t>454: source value from PTF - TRANSFERRING FACILITY (#45-21.1)</t>
+  </si>
+  <si>
     <t>Inpat.Census.TransferringFacility
 Inpat.Inpatient.TransferFromFacility
 Inpat.InpatientFeeBasis.TransferringFacility</t>
   </si>
   <si>
-    <t>454: source value from PTF - TRANSFERRING FACILITY (#45-21.1)</t>
-  </si>
-  <si>
     <t>Encounter.hospitalization.admitSource</t>
   </si>
   <si>
@@ -1630,6 +1638,9 @@
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>955: terminologyMaps using VF_SourceOfAdmission on PTF - SOURCE OF ADMISSION &gt; PRF CODE (#45-20 &gt; 45.1-.01)</t>
   </si>
   <si>
     <t>Inpat.Census.AdmitSourceIEN
@@ -1637,9 +1648,6 @@
 Inpat.InpatientFeeBasis.AdmitSourceIEN</t>
   </si>
   <si>
-    <t>955: terminologyMaps using VF_SourceOfAdmission on PTF - SOURCE OF ADMISSION &gt; PRF CODE (#45-20 &gt; 45.1-.01)</t>
-  </si>
-  <si>
     <t>Encounter.hospitalization.admitSource.coding.id</t>
   </si>
   <si>
@@ -1906,6 +1914,9 @@
   </si>
   <si>
     <t>Encounter.hospitalization.destination.display</t>
+  </si>
+  <si>
+    <t>455: source value from PTF - RECEIVING FACILITY (#45-76.1)</t>
   </si>
   <si>
     <t>Inpat.Census.ReceivingFacility
@@ -1913,9 +1924,6 @@
 Inpat.InpatientFeeBasis.ReceivingFacility</t>
   </si>
   <si>
-    <t>455: source value from PTF - RECEIVING FACILITY (#45-76.1)</t>
-  </si>
-  <si>
     <t>Encounter.hospitalization.dischargeDisposition</t>
   </si>
   <si>
@@ -1935,6 +1943,9 @@
   </si>
   <si>
     <t>PV1-36</t>
+  </si>
+  <si>
+    <t>456: source value from PTF - PLACE OF DISPOSITION (#45-75)</t>
   </si>
   <si>
     <t>Inpat.Census.PlaceOfDispositionIEN
@@ -1942,9 +1953,6 @@
 Inpat.InpatientFeeBasis.PlaceOfDispositionIEN</t>
   </si>
   <si>
-    <t>456: source value from PTF - PLACE OF DISPOSITION (#45-75)</t>
-  </si>
-  <si>
     <t>Encounter.location</t>
   </si>
   <si>
@@ -1989,14 +1997,14 @@
   </si>
   <si>
     <t>PV1-3 / PV1-6 / PV1-11 / PV1-42 / PV1-43</t>
+  </si>
+  <si>
+    <t>461: reference from PTF - FACILITY (#45-3)</t>
   </si>
   <si>
     <t>Inpat.Census.DischargeFacility
 Inpat.Inpatient.DischargeFromFacility
 Inpat.InpatientFeeBasis.DischargeFacility</t>
-  </si>
-  <si>
-    <t>461: reference from PTF - FACILITY (#45-3)</t>
   </si>
   <si>
     <t>Encounter.location.status</t>
@@ -2450,8 +2458,8 @@
     <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="191.1328125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="56.453125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="110.4140625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="110.4140625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="56.453125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4841,33 +4849,33 @@
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>228</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4890,16 +4898,16 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4949,7 +4957,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4984,10 +4992,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5102,10 +5110,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5222,14 +5230,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5251,10 +5259,10 @@
         <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>139</v>
@@ -5309,7 +5317,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5344,10 +5352,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5427,7 +5435,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>90</v>
@@ -5462,10 +5470,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5491,10 +5499,10 @@
         <v>208</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5545,7 +5553,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>90</v>
@@ -5580,10 +5588,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5606,13 +5614,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5642,10 +5650,10 @@
         <v>183</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5663,7 +5671,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>90</v>
@@ -5675,33 +5683,33 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>257</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5724,13 +5732,13 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5781,7 +5789,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5816,10 +5824,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5934,10 +5942,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6054,14 +6062,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -6083,10 +6091,10 @@
         <v>136</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>139</v>
@@ -6141,7 +6149,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6176,10 +6184,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6202,13 +6210,13 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6238,10 +6246,10 @@
         <v>183</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -6259,7 +6267,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>90</v>
@@ -6294,10 +6302,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6323,10 +6331,10 @@
         <v>208</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6377,7 +6385,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>90</v>
@@ -6412,10 +6420,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6441,13 +6449,13 @@
         <v>178</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6476,10 +6484,10 @@
         <v>183</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6497,7 +6505,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6512,16 +6520,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6532,10 +6540,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6561,10 +6569,10 @@
         <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6591,13 +6599,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6615,7 +6623,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6630,7 +6638,7 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>160</v>
@@ -6639,7 +6647,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6650,10 +6658,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6679,10 +6687,10 @@
         <v>178</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6709,31 +6717,31 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6751,13 +6759,13 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6768,14 +6776,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6794,16 +6802,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6853,7 +6861,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6868,30 +6876,30 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6914,13 +6922,13 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6971,7 +6979,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6986,16 +6994,16 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>160</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7006,14 +7014,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7032,13 +7040,13 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7089,7 +7097,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7104,10 +7112,10 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
@@ -7124,10 +7132,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7150,13 +7158,13 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7207,7 +7215,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7222,16 +7230,16 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7242,10 +7250,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7360,10 +7368,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7480,14 +7488,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7509,10 +7517,10 @@
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>139</v>
@@ -7567,7 +7575,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7602,10 +7610,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7631,13 +7639,13 @@
         <v>178</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7666,28 +7674,28 @@
         <v>183</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7702,16 +7710,16 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7722,10 +7730,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7751,10 +7759,10 @@
         <v>208</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7805,7 +7813,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7823,13 +7831,13 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7840,10 +7848,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7866,13 +7874,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7923,7 +7931,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7938,30 +7946,30 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7984,13 +7992,13 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8041,7 +8049,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8056,16 +8064,16 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8076,10 +8084,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8105,13 +8113,13 @@
         <v>208</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8161,7 +8169,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8176,16 +8184,16 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8196,10 +8204,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8314,10 +8322,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8434,10 +8442,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8460,16 +8468,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8519,7 +8527,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8528,7 +8536,7 @@
         <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>102</v>
@@ -8537,27 +8545,27 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8580,23 +8588,23 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="R52" t="s" s="2">
         <v>82</v>
@@ -8641,7 +8649,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8650,7 +8658,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -8659,27 +8667,27 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>232</v>
+        <v>389</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>387</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8702,16 +8710,16 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8761,7 +8769,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8776,16 +8784,16 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8796,14 +8804,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8825,13 +8833,13 @@
         <v>178</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8860,10 +8868,10 @@
         <v>114</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8881,7 +8889,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8896,34 +8904,34 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8942,16 +8950,16 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9001,7 +9009,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9016,16 +9024,16 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9036,10 +9044,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9062,13 +9070,13 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9119,7 +9127,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9137,7 +9145,7 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>82</v>
@@ -9154,10 +9162,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9272,10 +9280,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9392,14 +9400,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9421,10 +9429,10 @@
         <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>139</v>
@@ -9479,7 +9487,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9514,14 +9522,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9540,16 +9548,16 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9599,7 +9607,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>90</v>
@@ -9614,16 +9622,16 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9634,10 +9642,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9663,10 +9671,10 @@
         <v>178</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9696,10 +9704,10 @@
         <v>114</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9717,7 +9725,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9752,10 +9760,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9778,13 +9786,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9835,7 +9843,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9853,7 +9861,7 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>82</v>
@@ -9870,10 +9878,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9896,16 +9904,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9955,7 +9963,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9973,7 +9981,7 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
@@ -9990,10 +9998,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10016,16 +10024,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10075,7 +10083,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10093,7 +10101,7 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>82</v>
@@ -10110,10 +10118,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10228,10 +10236,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10348,14 +10356,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10377,10 +10385,10 @@
         <v>136</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>139</v>
@@ -10435,7 +10443,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10470,10 +10478,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10499,10 +10507,10 @@
         <v>148</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10553,7 +10561,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10577,7 +10585,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10588,10 +10596,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10614,13 +10622,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10671,7 +10679,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10689,7 +10697,7 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>82</v>
@@ -10706,10 +10714,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10824,10 +10832,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10944,10 +10952,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10973,13 +10981,13 @@
         <v>156</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11029,7 +11037,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11038,7 +11046,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -11064,10 +11072,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11093,13 +11101,13 @@
         <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11128,10 +11136,10 @@
         <v>183</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11149,7 +11157,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11184,10 +11192,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11213,13 +11221,13 @@
         <v>148</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11269,7 +11277,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11287,7 +11295,7 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>82</v>
@@ -11304,10 +11312,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11333,13 +11341,13 @@
         <v>156</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11389,7 +11397,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11416,18 +11424,18 @@
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11453,10 +11461,10 @@
         <v>178</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11486,10 +11494,10 @@
         <v>114</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11507,7 +11515,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11525,13 +11533,13 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11542,10 +11550,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11660,10 +11668,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11780,10 +11788,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11806,19 +11814,19 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11847,7 +11855,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11865,7 +11873,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11883,27 +11891,27 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12018,10 +12026,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12138,10 +12146,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12167,16 +12175,16 @@
         <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12225,7 +12233,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12243,13 +12251,13 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12260,10 +12268,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12289,13 +12297,13 @@
         <v>156</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12345,7 +12353,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12363,13 +12371,13 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12380,10 +12388,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12409,14 +12417,14 @@
         <v>110</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12465,7 +12473,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12483,27 +12491,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>505</v>
+        <v>533</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>531</v>
+        <v>508</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12529,14 +12537,14 @@
         <v>156</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12585,7 +12593,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12603,13 +12611,13 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12620,10 +12628,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12646,19 +12654,19 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12707,7 +12715,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12725,13 +12733,13 @@
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12742,10 +12750,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12771,16 +12779,16 @@
         <v>156</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12829,7 +12837,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12847,13 +12855,13 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12864,10 +12872,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12893,10 +12901,10 @@
         <v>178</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12923,13 +12931,13 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12947,7 +12955,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12971,7 +12979,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12982,10 +12990,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13011,16 +13019,16 @@
         <v>178</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13045,13 +13053,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -13069,7 +13077,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13087,13 +13095,13 @@
         <v>82</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13104,10 +13112,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13133,10 +13141,10 @@
         <v>178</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13166,10 +13174,10 @@
         <v>114</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13187,7 +13195,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13205,13 +13213,13 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13222,10 +13230,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13251,10 +13259,10 @@
         <v>178</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13284,10 +13292,10 @@
         <v>114</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13305,7 +13313,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13323,13 +13331,13 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13340,10 +13348,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13366,13 +13374,13 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13423,7 +13431,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13441,13 +13449,13 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13458,10 +13466,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13576,10 +13584,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13696,10 +13704,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13725,13 +13733,13 @@
         <v>156</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13781,7 +13789,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13790,7 +13798,7 @@
         <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>102</v>
@@ -13816,10 +13824,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13845,13 +13853,13 @@
         <v>104</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13880,10 +13888,10 @@
         <v>183</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -13901,7 +13909,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13936,10 +13944,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13965,13 +13973,13 @@
         <v>148</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14021,7 +14029,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14039,7 +14047,7 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>82</v>
@@ -14056,10 +14064,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14085,13 +14093,13 @@
         <v>156</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14141,7 +14149,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14168,18 +14176,18 @@
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14205,10 +14213,10 @@
         <v>178</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14238,10 +14246,10 @@
         <v>114</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -14259,7 +14267,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14277,27 +14285,27 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14320,16 +14328,16 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14379,7 +14387,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14397,7 +14405,7 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>82</v>
@@ -14414,10 +14422,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14532,10 +14540,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14652,14 +14660,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14681,10 +14689,10 @@
         <v>136</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>139</v>
@@ -14739,7 +14747,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14774,10 +14782,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14800,13 +14808,13 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14857,7 +14865,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>90</v>
@@ -14872,30 +14880,30 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14921,13 +14929,13 @@
         <v>110</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14956,10 +14964,10 @@
         <v>172</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -14977,7 +14985,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14995,7 +15003,7 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>82</v>
@@ -15012,10 +15020,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15041,13 +15049,13 @@
         <v>178</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15073,13 +15081,13 @@
         <v>82</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>82</v>
@@ -15097,7 +15105,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15132,10 +15140,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15161,10 +15169,10 @@
         <v>208</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15215,7 +15223,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15233,7 +15241,7 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
@@ -15250,10 +15258,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15276,13 +15284,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15333,7 +15341,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15348,30 +15356,30 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>82</v>
+        <v>648</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>646</v>
+        <v>82</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15394,16 +15402,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15453,7 +15461,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15468,10 +15476,10 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -727,7 +727,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-5:435: fixed value "finished" {null}</t>
+inv-6:435: fixed value = finished if PTF - DISCHARGE DATE (#45-70) case not null {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -835,7 +835,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-4:1601: fixed value "http://terminology.hl7.org/CodeSystem/v3-ActCode|IMP" {null}</t>
+inv-5:1601: fixed value = http://terminology.hl7.org/CodeSystem/v3-ActCode|IMP {null}</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4155" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4155" uniqueCount="658">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -727,7 +727,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-6:435: fixed value = finished if PTF - DISCHARGE DATE (#45-70) case not null {null}</t>
+inv-7:435: fixed value = finished if PTF - DISCHARGE DATE (#45-70) case not null {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -835,7 +835,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-5:1601: fixed value = http://terminology.hl7.org/CodeSystem/v3-ActCode|IMP {null}</t>
+inv-6:1601: fixed value = http://terminology.hl7.org/CodeSystem/v3-ActCode|IMP {null}</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -911,6 +911,12 @@
   </si>
   <si>
     <t>PV1-4 / PV1-18</t>
+  </si>
+  <si>
+    <t>1616: source value from INPATIENT CPT CODE - CPT CODE &gt; CPT (#46-.01 &gt; 81-)</t>
+  </si>
+  <si>
+    <t>Inpat.InpatientCPTProcedure.CPTIEN</t>
   </si>
   <si>
     <t>Encounter.serviceType</t>
@@ -6532,18 +6538,18 @@
         <v>282</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6569,10 +6575,10 @@
         <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6599,13 +6605,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6623,7 +6629,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6647,7 +6653,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6658,10 +6664,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6687,10 +6693,10 @@
         <v>178</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6717,31 +6723,31 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6759,13 +6765,13 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6776,14 +6782,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6802,16 +6808,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6861,7 +6867,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6876,30 +6882,30 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6922,13 +6928,13 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6979,7 +6985,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6994,16 +7000,16 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>160</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7014,14 +7020,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7040,13 +7046,13 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7097,7 +7103,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7112,10 +7118,10 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
@@ -7132,10 +7138,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7161,10 +7167,10 @@
         <v>236</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7215,7 +7221,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7230,16 +7236,16 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7250,10 +7256,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7368,10 +7374,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7488,10 +7494,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7610,10 +7616,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7639,13 +7645,13 @@
         <v>178</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7674,28 +7680,28 @@
         <v>183</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7710,16 +7716,16 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7730,10 +7736,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7759,10 +7765,10 @@
         <v>208</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7813,7 +7819,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7831,13 +7837,13 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7848,10 +7854,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7874,13 +7880,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7931,7 +7937,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7946,19 +7952,19 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7966,10 +7972,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7992,13 +7998,13 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8049,7 +8055,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8064,16 +8070,16 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8084,10 +8090,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8113,13 +8119,13 @@
         <v>208</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8169,7 +8175,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8184,16 +8190,16 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8204,10 +8210,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8322,10 +8328,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8442,10 +8448,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8468,16 +8474,16 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8527,7 +8533,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8536,7 +8542,7 @@
         <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>102</v>
@@ -8545,27 +8551,27 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8588,23 +8594,23 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="R52" t="s" s="2">
         <v>82</v>
@@ -8649,7 +8655,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8658,7 +8664,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -8667,16 +8673,16 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>234</v>
@@ -8684,10 +8690,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8710,16 +8716,16 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8769,7 +8775,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8784,16 +8790,16 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8804,14 +8810,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8833,13 +8839,13 @@
         <v>178</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8868,10 +8874,10 @@
         <v>114</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8889,7 +8895,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8904,34 +8910,34 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8950,16 +8956,16 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9009,7 +9015,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9024,16 +9030,16 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9044,10 +9050,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9073,10 +9079,10 @@
         <v>236</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9127,7 +9133,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9145,7 +9151,7 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>82</v>
@@ -9162,10 +9168,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9280,10 +9286,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9400,10 +9406,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9522,14 +9528,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9548,16 +9554,16 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9607,7 +9613,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>90</v>
@@ -9622,16 +9628,16 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9642,10 +9648,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9671,10 +9677,10 @@
         <v>178</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9704,10 +9710,10 @@
         <v>114</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9725,7 +9731,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9760,10 +9766,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9786,13 +9792,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9843,7 +9849,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9861,7 +9867,7 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>82</v>
@@ -9878,10 +9884,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9904,16 +9910,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9963,7 +9969,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9981,7 +9987,7 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
@@ -9998,10 +10004,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10027,13 +10033,13 @@
         <v>236</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10083,7 +10089,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10101,7 +10107,7 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>82</v>
@@ -10118,10 +10124,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10236,10 +10242,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10356,10 +10362,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10478,10 +10484,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10507,10 +10513,10 @@
         <v>148</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10561,7 +10567,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10585,7 +10591,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10596,10 +10602,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10622,13 +10628,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10679,7 +10685,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10697,7 +10703,7 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>82</v>
@@ -10714,10 +10720,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10832,10 +10838,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10952,10 +10958,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10981,13 +10987,13 @@
         <v>156</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11037,7 +11043,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11046,7 +11052,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -11072,10 +11078,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11101,13 +11107,13 @@
         <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11136,10 +11142,10 @@
         <v>183</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11157,7 +11163,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11192,10 +11198,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11221,13 +11227,13 @@
         <v>148</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11277,7 +11283,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11295,7 +11301,7 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>82</v>
@@ -11312,10 +11318,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11341,13 +11347,13 @@
         <v>156</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11397,7 +11403,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11424,18 +11430,18 @@
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11461,10 +11467,10 @@
         <v>178</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11494,10 +11500,10 @@
         <v>114</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11515,7 +11521,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11533,13 +11539,13 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11550,10 +11556,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11668,10 +11674,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11788,10 +11794,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11817,16 +11823,16 @@
         <v>252</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11855,7 +11861,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11873,7 +11879,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11891,27 +11897,27 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12026,10 +12032,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12146,10 +12152,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12175,16 +12181,16 @@
         <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12233,7 +12239,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12251,13 +12257,13 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12268,10 +12274,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12297,13 +12303,13 @@
         <v>156</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12353,7 +12359,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12371,13 +12377,13 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12388,10 +12394,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12417,14 +12423,14 @@
         <v>110</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12473,7 +12479,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12491,27 +12497,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12537,14 +12543,14 @@
         <v>156</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12593,7 +12599,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12611,13 +12617,13 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12628,10 +12634,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12654,19 +12660,19 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12715,7 +12721,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12733,13 +12739,13 @@
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12750,10 +12756,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12779,16 +12785,16 @@
         <v>156</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12837,7 +12843,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12855,13 +12861,13 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12872,10 +12878,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12901,10 +12907,10 @@
         <v>178</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12931,13 +12937,13 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12955,7 +12961,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12979,7 +12985,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12990,10 +12996,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13019,16 +13025,16 @@
         <v>178</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13053,13 +13059,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -13077,7 +13083,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13095,13 +13101,13 @@
         <v>82</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13112,10 +13118,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13141,10 +13147,10 @@
         <v>178</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13174,10 +13180,10 @@
         <v>114</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13195,7 +13201,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13213,13 +13219,13 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13230,10 +13236,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13259,10 +13265,10 @@
         <v>178</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13292,10 +13298,10 @@
         <v>114</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13313,7 +13319,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13331,13 +13337,13 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13348,10 +13354,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13374,13 +13380,13 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13431,7 +13437,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13449,13 +13455,13 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13466,10 +13472,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13584,10 +13590,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13704,10 +13710,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13733,13 +13739,13 @@
         <v>156</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13789,7 +13795,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13798,7 +13804,7 @@
         <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>102</v>
@@ -13824,10 +13830,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13853,13 +13859,13 @@
         <v>104</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13888,10 +13894,10 @@
         <v>183</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -13909,7 +13915,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13944,10 +13950,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13973,13 +13979,13 @@
         <v>148</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14029,7 +14035,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14047,7 +14053,7 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>82</v>
@@ -14064,10 +14070,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14093,13 +14099,13 @@
         <v>156</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14149,7 +14155,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14176,18 +14182,18 @@
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14213,10 +14219,10 @@
         <v>178</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14246,10 +14252,10 @@
         <v>114</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -14267,7 +14273,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14285,27 +14291,27 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14331,13 +14337,13 @@
         <v>236</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14387,7 +14393,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14405,7 +14411,7 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>82</v>
@@ -14422,10 +14428,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14540,10 +14546,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14660,10 +14666,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14782,10 +14788,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14808,13 +14814,13 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14865,7 +14871,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>90</v>
@@ -14880,30 +14886,30 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14929,13 +14935,13 @@
         <v>110</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14964,10 +14970,10 @@
         <v>172</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -14985,7 +14991,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15003,7 +15009,7 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>82</v>
@@ -15020,10 +15026,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15049,13 +15055,13 @@
         <v>178</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15081,13 +15087,13 @@
         <v>82</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>82</v>
@@ -15105,7 +15111,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15140,10 +15146,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15169,10 +15175,10 @@
         <v>208</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15223,7 +15229,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15241,7 +15247,7 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
@@ -15258,10 +15264,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15284,13 +15290,13 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15341,7 +15347,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15356,30 +15362,30 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>82</v>
+        <v>627</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15402,16 +15408,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15461,7 +15467,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15476,10 +15482,10 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterInpatientPTF.xlsx
+++ b/docs/StructureDefinition-EncounterInpatientPTF.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
